--- a/excel-files/CALOOCAN/KAUNLARAN ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/CALOOCAN/KAUNLARAN ELEMENTARY SCHOOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="168" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC8EC51F-A4E9-4349-964B-6C26EF88F600}"/>
+  <xr:revisionPtr revIDLastSave="181" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71FC666C-2A58-4224-8ED4-6CA25CD03CA6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -80,6 +80,9 @@
   </si>
   <si>
     <t>Math</t>
+  </si>
+  <si>
+    <t>RO</t>
   </si>
   <si>
     <t>Science</t>
@@ -745,6 +748,15 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -756,15 +768,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3733,17 +3736,21 @@
         <v>462</v>
       </c>
       <c r="D11" s="1">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
+        <v>631</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
-        <v>462</v>
+        <v>0</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
-        <v>0</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="19.5">
@@ -3852,7 +3859,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1">
         <v>522</v>
@@ -3934,7 +3941,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" s="1">
         <v>556</v>
@@ -3962,7 +3969,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22" s="1">
         <v>556</v>
@@ -4046,7 +4053,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C25" s="1">
         <v>556</v>
@@ -4074,7 +4081,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>556</v>
@@ -4102,7 +4109,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C27" s="1">
         <v>556</v>
@@ -4130,7 +4137,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C28" s="1">
         <v>556</v>
@@ -4154,7 +4161,7 @@
         <v>4</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C29" s="1">
         <v>556</v>
@@ -4188,7 +4195,7 @@
         <v>5</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C31" s="1">
         <v>476</v>
@@ -4216,7 +4223,7 @@
         <v>5</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1">
         <v>476</v>
@@ -4288,7 +4295,7 @@
         <v>5</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C35" s="1">
         <v>476</v>
@@ -4316,7 +4323,7 @@
         <v>5</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C36" s="1">
         <v>476</v>
@@ -4344,7 +4351,7 @@
         <v>5</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C37" s="1">
         <v>476</v>
@@ -4372,7 +4379,7 @@
         <v>5</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C38" s="1">
         <v>476</v>
@@ -4396,7 +4403,7 @@
         <v>5</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C39" s="1">
         <v>476</v>
@@ -4430,7 +4437,7 @@
         <v>6</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C41" s="1">
         <v>535</v>
@@ -4454,7 +4461,7 @@
         <v>6</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C42" s="1">
         <v>535</v>
@@ -4526,7 +4533,7 @@
         <v>6</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C45" s="1">
         <v>535</v>
@@ -4550,7 +4557,7 @@
         <v>6</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C46" s="1">
         <v>535</v>
@@ -4574,7 +4581,7 @@
         <v>6</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C47" s="1">
         <v>535</v>
@@ -4598,7 +4605,7 @@
         <v>6</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C48" s="1">
         <v>535</v>
@@ -4622,7 +4629,7 @@
         <v>6</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C49" s="1">
         <v>535</v>
@@ -4642,14 +4649,14 @@
       </c>
     </row>
     <row r="50" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A50" s="46"/>
-      <c r="B50" s="47"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="46"/>
-      <c r="E50" s="46"/>
-      <c r="F50" s="46"/>
-      <c r="G50" s="48"/>
-      <c r="H50" s="48"/>
+      <c r="A50" s="42"/>
+      <c r="B50" s="43"/>
+      <c r="C50" s="42"/>
+      <c r="D50" s="42"/>
+      <c r="E50" s="42"/>
+      <c r="F50" s="42"/>
+      <c r="G50" s="44"/>
+      <c r="H50" s="44"/>
     </row>
     <row r="51" spans="1:8" ht="27.75" customHeight="1">
       <c r="A51" s="7"/>
@@ -4666,7 +4673,7 @@
         <v>7</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
@@ -4686,7 +4693,7 @@
         <v>7</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="10"/>
@@ -4726,7 +4733,7 @@
         <v>7</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="10"/>
@@ -4746,7 +4753,7 @@
         <v>7</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
@@ -4766,7 +4773,7 @@
         <v>7</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="10"/>
@@ -4786,7 +4793,7 @@
         <v>7</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C58" s="10"/>
       <c r="D58" s="10"/>
@@ -4806,7 +4813,7 @@
         <v>7</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="10"/>
@@ -4826,7 +4833,7 @@
         <v>7</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C60" s="10"/>
       <c r="D60" s="10"/>
@@ -4856,7 +4863,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
@@ -4876,7 +4883,7 @@
         <v>8</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="10"/>
@@ -4916,7 +4923,7 @@
         <v>8</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
@@ -4936,7 +4943,7 @@
         <v>8</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
@@ -4956,7 +4963,7 @@
         <v>8</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="10"/>
@@ -4976,7 +4983,7 @@
         <v>8</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="10"/>
@@ -4996,7 +5003,7 @@
         <v>8</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="10"/>
@@ -5016,7 +5023,7 @@
         <v>8</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="10"/>
@@ -5046,7 +5053,7 @@
         <v>9</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
@@ -5066,7 +5073,7 @@
         <v>9</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="10"/>
@@ -5106,7 +5113,7 @@
         <v>9</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
@@ -5126,7 +5133,7 @@
         <v>9</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
@@ -5146,7 +5153,7 @@
         <v>9</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="10"/>
@@ -5166,7 +5173,7 @@
         <v>9</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="10"/>
@@ -5186,7 +5193,7 @@
         <v>9</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="10"/>
@@ -5206,7 +5213,7 @@
         <v>9</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="10"/>
@@ -5236,7 +5243,7 @@
         <v>10</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
@@ -5256,7 +5263,7 @@
         <v>10</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="10"/>
@@ -5296,7 +5303,7 @@
         <v>10</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="10"/>
@@ -5316,7 +5323,7 @@
         <v>10</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
@@ -5336,7 +5343,7 @@
         <v>10</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
@@ -5356,7 +5363,7 @@
         <v>10</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="10"/>
@@ -5376,7 +5383,7 @@
         <v>10</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="10"/>
@@ -5396,7 +5403,7 @@
         <v>10</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C90" s="10"/>
       <c r="D90" s="10"/>
@@ -5423,10 +5430,10 @@
     </row>
     <row r="92" spans="1:8" ht="27.75" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
@@ -5443,10 +5450,10 @@
     </row>
     <row r="93" spans="1:8" ht="27.75" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
@@ -5463,10 +5470,10 @@
     </row>
     <row r="94" spans="1:8" ht="27.75" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
@@ -5483,10 +5490,10 @@
     </row>
     <row r="95" spans="1:8" ht="40.5" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
@@ -5503,10 +5510,10 @@
     </row>
     <row r="96" spans="1:8" ht="38.25" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
@@ -5523,10 +5530,10 @@
     </row>
     <row r="97" spans="1:8" ht="27.75" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
@@ -5543,10 +5550,10 @@
     </row>
     <row r="98" spans="1:8" ht="47.25" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
@@ -5563,10 +5570,10 @@
     </row>
     <row r="99" spans="1:8" ht="38.25">
       <c r="A99" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
@@ -5588,8 +5595,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E52:E60 E62:E70 E2:E6 E72:E80 E82:E90 E8:E12 E92:E99 E41:E50" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E92:E99 E82:E90 E72:E80 E62:E70 E52:E60 E41:E50 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F92:F99 F31:F39 F52:F60 F62:F70 F72:F80 F82:F90 F2:F6 F8:F12 F21:F29 F41:F50" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5634,38 +5641,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43" t="s">
+      <c r="D1" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="44" t="s">
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="45" t="s">
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5678,81 +5685,81 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M2" s="40" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N2" s="40" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O2" s="22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R2" s="25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="U2" s="24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Y2" s="41" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Z2" s="41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AA2" s="26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="30.6" customHeight="1">
       <c r="A3" s="39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="32">
@@ -6191,7 +6198,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1">
         <v>431</v>
@@ -6262,7 +6269,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1">
         <v>431</v>
@@ -6333,7 +6340,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12" s="1">
         <v>431</v>
@@ -6772,7 +6779,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" s="1">
         <v>462</v>
@@ -6847,7 +6854,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1">
         <v>462</v>
@@ -6918,7 +6925,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C21" s="1">
         <v>462</v>
@@ -7216,7 +7223,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>522</v>
@@ -7435,7 +7442,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" s="1">
         <v>522</v>
@@ -7508,7 +7515,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C30" s="1">
         <v>522</v>
@@ -7579,7 +7586,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C31" s="1">
         <v>522</v>
@@ -7664,7 +7671,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C33" s="1">
         <v>556</v>
@@ -7735,7 +7742,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C34" s="1">
         <v>556</v>
@@ -7948,7 +7955,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C37" s="1">
         <v>556</v>
@@ -8019,7 +8026,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C38" s="1">
         <v>556</v>
@@ -8090,7 +8097,7 @@
         <v>4</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C39" s="1">
         <v>556</v>
@@ -8161,7 +8168,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C40" s="1">
         <v>556</v>
@@ -8232,7 +8239,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C41" s="1">
         <v>556</v>
@@ -8317,7 +8324,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1">
         <v>476</v>
@@ -8390,7 +8397,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1">
         <v>476</v>
@@ -8609,7 +8616,7 @@
         <v>5</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C47" s="1">
         <v>476</v>
@@ -8680,7 +8687,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1">
         <v>476</v>
@@ -8753,7 +8760,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C49" s="1">
         <v>476</v>
@@ -8824,7 +8831,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C50" s="1">
         <v>476</v>
@@ -8897,7 +8904,7 @@
         <v>5</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C51" s="1">
         <v>476</v>
@@ -8982,7 +8989,7 @@
         <v>6</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C53" s="1">
         <v>535</v>
@@ -9053,7 +9060,7 @@
         <v>6</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C54" s="1">
         <v>535</v>
@@ -9266,7 +9273,7 @@
         <v>6</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C57" s="1">
         <v>535</v>
@@ -9337,7 +9344,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C58" s="1">
         <v>535</v>
@@ -9408,7 +9415,7 @@
         <v>6</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C59" s="1">
         <v>535</v>
@@ -9479,7 +9486,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C60" s="1">
         <v>535</v>
@@ -9550,7 +9557,7 @@
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C61" s="1">
         <v>535</v>
@@ -9709,7 +9716,7 @@
         <v>7</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C64" s="10"/>
       <c r="D64" s="12">
@@ -9778,7 +9785,7 @@
         <v>7</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="12">
@@ -9916,7 +9923,7 @@
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="12">
@@ -9985,7 +9992,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -10054,7 +10061,7 @@
         <v>7</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="12">
@@ -10123,7 +10130,7 @@
         <v>7</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="12">
@@ -10192,7 +10199,7 @@
         <v>7</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="12">
@@ -10261,7 +10268,7 @@
         <v>7</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="12">
@@ -10359,7 +10366,7 @@
         <v>8</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -10428,7 +10435,7 @@
         <v>8</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="12">
@@ -10566,7 +10573,7 @@
         <v>8</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="12">
@@ -10635,7 +10642,7 @@
         <v>8</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="12">
@@ -10704,7 +10711,7 @@
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="12">
@@ -10773,7 +10780,7 @@
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -10842,7 +10849,7 @@
         <v>8</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="12">
@@ -10911,7 +10918,7 @@
         <v>8</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="12">
@@ -11009,7 +11016,7 @@
         <v>9</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -11078,7 +11085,7 @@
         <v>9</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="12">
@@ -11216,7 +11223,7 @@
         <v>9</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="12">
@@ -11285,7 +11292,7 @@
         <v>9</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="12">
@@ -11354,7 +11361,7 @@
         <v>9</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="12">
@@ -11423,7 +11430,7 @@
         <v>9</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C90" s="10"/>
       <c r="D90" s="12">
@@ -11492,7 +11499,7 @@
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="12">
@@ -11561,7 +11568,7 @@
         <v>9</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C92" s="10"/>
       <c r="D92" s="12">
@@ -11659,7 +11666,7 @@
         <v>10</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -11728,7 +11735,7 @@
         <v>10</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="12">
@@ -11866,7 +11873,7 @@
         <v>10</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="12">
@@ -11935,7 +11942,7 @@
         <v>10</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -12004,7 +12011,7 @@
         <v>10</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="12">
@@ -12073,7 +12080,7 @@
         <v>10</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -12142,7 +12149,7 @@
         <v>10</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="12">
@@ -12211,7 +12218,7 @@
         <v>10</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C102" s="10"/>
       <c r="D102" s="12">
@@ -12306,10 +12313,10 @@
     </row>
     <row r="104" spans="1:27" ht="38.25">
       <c r="A104" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="5">
@@ -12375,10 +12382,10 @@
     </row>
     <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="5">
@@ -12444,10 +12451,10 @@
     </row>
     <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="5">
@@ -12513,10 +12520,10 @@
     </row>
     <row r="107" spans="1:27" ht="19.5">
       <c r="A107" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="5">
@@ -12582,10 +12589,10 @@
     </row>
     <row r="108" spans="1:27" ht="38.25">
       <c r="A108" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="5">
@@ -12651,10 +12658,10 @@
     </row>
     <row r="109" spans="1:27" ht="38.25">
       <c r="A109" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="5">
@@ -12720,10 +12727,10 @@
     </row>
     <row r="110" spans="1:27" ht="57.75">
       <c r="A110" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="5">
@@ -12789,10 +12796,10 @@
     </row>
     <row r="111" spans="1:27" s="7" customFormat="1" ht="38.25">
       <c r="A111" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C111" s="1"/>
       <c r="D111" s="5">
@@ -13874,186 +13881,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="10:10" ht="15">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10" ht="15">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10" ht="15">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10" ht="15">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10" ht="15">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10" ht="15">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10" ht="15">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10" ht="15">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10" ht="15">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10" ht="15">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10" ht="15">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10" ht="15">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10" ht="15">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10" ht="15">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10" ht="15">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10" ht="15">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10" ht="15">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10" ht="15">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10" ht="15">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10" ht="15">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10" ht="15">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10" ht="15">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10" ht="15">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10" ht="15">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10" ht="15">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10" ht="15">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10" ht="15">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10" ht="15">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10" ht="15">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10" ht="15">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
+    <row r="129" ht="15"/>
+    <row r="130" ht="15"/>
+    <row r="131" ht="15"/>
+    <row r="132" ht="15"/>
+    <row r="133" ht="15"/>
+    <row r="134" ht="15"/>
+    <row r="135" ht="15"/>
+    <row r="136" ht="15"/>
+    <row r="137" ht="15"/>
+    <row r="138" ht="15"/>
+    <row r="139" ht="15"/>
+    <row r="140" ht="15"/>
+    <row r="141" ht="15"/>
+    <row r="142" ht="15"/>
+    <row r="143" ht="15"/>
+    <row r="144" ht="15"/>
+    <row r="145" ht="15"/>
+    <row r="146" ht="15"/>
+    <row r="147" ht="15"/>
+    <row r="148" ht="15"/>
+    <row r="149" ht="15"/>
+    <row r="150" ht="15"/>
+    <row r="151" ht="15"/>
+    <row r="152" ht="15"/>
+    <row r="153" ht="15"/>
+    <row r="154" ht="15"/>
+    <row r="155" ht="15"/>
+    <row r="156" ht="15"/>
+    <row r="157" ht="15"/>
+    <row r="158" ht="15"/>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C64:C72 C74:C82 C84:C92 C94:C102 C104:C111 C113:C128 C5:C12 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C62" name="Textbooks"/>
@@ -14071,8 +13928,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S113:S128 M113:M128 Y113:Y128 G113:G128" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X64:X72 X74:X82 L113:L128 X84:X92 X94:X102 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L64:L72 L74:L82 R113:R128 L84:L92 L94:L102 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R64:R72 R74:R82 F113:F128 R84:R92 R94:R102 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F64:F72 F74:F82 F5:F12 F84:F92 F94:F102 F14:F21 F104:F111 R104:R111 L104:L111 X104:X111 X113:X128 X53:X62 L53:L62 R53:R62 F53:F62" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X113:X128 X104:X111 X84:X92 X74:X82 X64:X72 X53:X62 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12 X94:X102 F113:F128 F104:F111 F94:F102 F84:F92 F74:F82 F64:F72 F53:F62 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L113:L128 L104:L111 L94:L102 L84:L92 L74:L82 L64:L72 L53:L62 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R113:R128 R104:R111 R94:R102 R84:R92 R74:R82 R64:R72 R53:R62 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G64:G72 G74:G82 G84:G92 G94:G102 G104:G111 G53:G62 S4:S111 Y14:Y111 M14:M111" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -14120,38 +13977,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43" t="s">
+      <c r="D1" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="44" t="s">
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="45" t="s">
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -14164,76 +14021,76 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M2" s="40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N2" s="40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O2" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R2" s="25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U2" s="24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y2" s="41" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z2" s="41" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AA2" s="26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="42" customHeight="1">
@@ -14600,7 +14457,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1">
         <v>431</v>
@@ -14671,7 +14528,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1">
         <v>431</v>
@@ -14742,7 +14599,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" s="1">
         <v>431</v>
@@ -15169,7 +15026,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1">
         <v>462</v>
@@ -15240,7 +15097,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" s="1">
         <v>462</v>
@@ -15311,7 +15168,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C19" s="1">
         <v>462</v>
@@ -15596,7 +15453,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="1">
         <v>522</v>
@@ -15809,7 +15666,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C27" s="1">
         <v>522</v>
@@ -15880,7 +15737,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C28" s="1">
         <v>522</v>
@@ -15951,7 +15808,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C29" s="1">
         <v>522</v>
@@ -16023,7 +15880,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C31" s="1">
         <v>556</v>
@@ -16094,7 +15951,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1">
         <v>556</v>
@@ -16307,7 +16164,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C35" s="1">
         <v>556</v>
@@ -16378,7 +16235,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C36" s="1">
         <v>556</v>
@@ -16449,7 +16306,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C37" s="1">
         <v>556</v>
@@ -16520,7 +16377,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C38" s="1">
         <v>556</v>
@@ -16591,7 +16448,7 @@
         <v>4</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C39" s="1">
         <v>556</v>
@@ -16662,7 +16519,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C40" s="1">
         <v>556</v>
@@ -16733,7 +16590,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C41" s="1">
         <v>556</v>
@@ -16805,7 +16662,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1">
         <v>476</v>
@@ -16876,7 +16733,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1">
         <v>476</v>
@@ -17089,7 +16946,7 @@
         <v>5</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C47" s="1">
         <v>476</v>
@@ -17160,7 +17017,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1">
         <v>476</v>
@@ -17231,7 +17088,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C49" s="1">
         <v>476</v>
@@ -17302,7 +17159,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C50" s="1">
         <v>476</v>
@@ -17373,7 +17230,7 @@
         <v>5</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C51" s="1">
         <v>476</v>
@@ -17444,7 +17301,7 @@
         <v>5</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C52" s="1">
         <v>476</v>
@@ -17515,7 +17372,7 @@
         <v>5</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C53" s="1">
         <v>476</v>
@@ -17587,7 +17444,7 @@
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C55" s="1">
         <v>535</v>
@@ -17668,7 +17525,7 @@
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C56" s="1">
         <v>535</v>
@@ -17901,7 +17758,7 @@
         <v>6</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C59" s="1">
         <v>535</v>
@@ -17972,7 +17829,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C60" s="1">
         <v>535</v>
@@ -18043,7 +17900,7 @@
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C61" s="1">
         <v>535</v>
@@ -18114,7 +17971,7 @@
         <v>6</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C62" s="1">
         <v>535</v>
@@ -18185,7 +18042,7 @@
         <v>6</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C63" s="1">
         <v>535</v>
@@ -18256,7 +18113,7 @@
         <v>6</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C64" s="1">
         <v>535</v>
@@ -18327,7 +18184,7 @@
         <v>6</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C65" s="1">
         <v>535</v>
@@ -18399,7 +18256,7 @@
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="12">
@@ -18468,7 +18325,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -18606,7 +18463,7 @@
         <v>7</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="12">
@@ -18675,7 +18532,7 @@
         <v>7</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="12">
@@ -18744,7 +18601,7 @@
         <v>7</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="12">
@@ -18813,7 +18670,7 @@
         <v>7</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C73" s="12"/>
       <c r="D73" s="12">
@@ -18882,7 +18739,7 @@
         <v>7</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -18951,7 +18808,7 @@
         <v>7</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="12">
@@ -19020,7 +18877,7 @@
         <v>7</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C76" s="12"/>
       <c r="D76" s="12">
@@ -19089,7 +18946,7 @@
         <v>7</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="12">
@@ -19159,7 +19016,7 @@
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="12">
@@ -19228,7 +19085,7 @@
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -19366,7 +19223,7 @@
         <v>8</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="12">
@@ -19435,7 +19292,7 @@
         <v>8</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="12">
@@ -19504,7 +19361,7 @@
         <v>8</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -19573,7 +19430,7 @@
         <v>8</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C85" s="12"/>
       <c r="D85" s="12">
@@ -19642,7 +19499,7 @@
         <v>8</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="12">
@@ -19711,7 +19568,7 @@
         <v>8</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="12">
@@ -19780,7 +19637,7 @@
         <v>8</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C88" s="12"/>
       <c r="D88" s="12">
@@ -19849,7 +19706,7 @@
         <v>8</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="12">
@@ -19919,7 +19776,7 @@
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="12">
@@ -19988,7 +19845,7 @@
         <v>9</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C92" s="10"/>
       <c r="D92" s="12">
@@ -20126,7 +19983,7 @@
         <v>9</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -20195,7 +20052,7 @@
         <v>9</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="12">
@@ -20264,7 +20121,7 @@
         <v>9</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="12">
@@ -20333,7 +20190,7 @@
         <v>9</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="12">
@@ -20402,7 +20259,7 @@
         <v>9</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -20471,7 +20328,7 @@
         <v>9</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="12">
@@ -20540,7 +20397,7 @@
         <v>9</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -20609,7 +20466,7 @@
         <v>9</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="12">
@@ -20679,7 +20536,7 @@
         <v>10</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="12">
@@ -20748,7 +20605,7 @@
         <v>10</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C104" s="10"/>
       <c r="D104" s="12">
@@ -20886,7 +20743,7 @@
         <v>10</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C106" s="10"/>
       <c r="D106" s="12">
@@ -20955,7 +20812,7 @@
         <v>10</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="12">
@@ -21024,7 +20881,7 @@
         <v>10</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C108" s="10"/>
       <c r="D108" s="12">
@@ -21093,7 +20950,7 @@
         <v>10</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="12">
@@ -21162,7 +21019,7 @@
         <v>10</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C110" s="10"/>
       <c r="D110" s="12">
@@ -21231,7 +21088,7 @@
         <v>10</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="12">
@@ -21300,7 +21157,7 @@
         <v>10</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C112" s="10"/>
       <c r="D112" s="12">
@@ -21369,7 +21226,7 @@
         <v>10</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="12">
@@ -21436,10 +21293,10 @@
     <row r="114" spans="1:28" s="7" customFormat="1"/>
     <row r="115" spans="1:28" ht="38.450000000000003">
       <c r="A115" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="5">
@@ -21505,10 +21362,10 @@
     </row>
     <row r="116" spans="1:28" ht="19.149999999999999">
       <c r="A116" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="5">
@@ -21574,10 +21431,10 @@
     </row>
     <row r="117" spans="1:28" ht="19.149999999999999">
       <c r="A117" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="5">
@@ -21643,10 +21500,10 @@
     </row>
     <row r="118" spans="1:28" ht="19.149999999999999">
       <c r="A118" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="5">
@@ -21712,10 +21569,10 @@
     </row>
     <row r="119" spans="1:28" ht="38.450000000000003">
       <c r="A119" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="5">
@@ -21781,10 +21638,10 @@
     </row>
     <row r="120" spans="1:28" ht="19.149999999999999">
       <c r="A120" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="5">
@@ -21850,10 +21707,10 @@
     </row>
     <row r="121" spans="1:28" ht="38.450000000000003">
       <c r="A121" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="5">
@@ -21919,10 +21776,10 @@
     </row>
     <row r="122" spans="1:28" ht="38.450000000000003">
       <c r="A122" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="5">
@@ -22700,8 +22557,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10 F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
